--- a/week-01/EX4B_more_GTrends.xlsx
+++ b/week-01/EX4B_more_GTrends.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sultansimsek/Documents/DataAnalytics/week-01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3714B68C-BD11-FC4A-ABD6-379E46CF6982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DAF960C-D625-D447-AEAF-297BB8397D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14960" yWindow="760" windowWidth="15280" windowHeight="17140" activeTab="1" xr2:uid="{E02B2F94-3CB3-194B-9AFC-6C9F0F90A351}"/>
+    <workbookView xWindow="9400" yWindow="760" windowWidth="20840" windowHeight="17140" activeTab="2" xr2:uid="{E02B2F94-3CB3-194B-9AFC-6C9F0F90A351}"/>
   </bookViews>
   <sheets>
     <sheet name="by search term" sheetId="1" r:id="rId1"/>
     <sheet name="by quarter" sheetId="2" r:id="rId2"/>
+    <sheet name="quarterly correlation" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="73">
   <si>
     <t>Week #</t>
   </si>
@@ -220,6 +221,42 @@
   </si>
   <si>
     <t>Quarter</t>
+  </si>
+  <si>
+    <t>Q1 - hamburger</t>
+  </si>
+  <si>
+    <t>Q1 - milkshake</t>
+  </si>
+  <si>
+    <t>Q2 - hamburger</t>
+  </si>
+  <si>
+    <t>Q2 - milkshake</t>
+  </si>
+  <si>
+    <t>Q3 - hamburger</t>
+  </si>
+  <si>
+    <t>Q4 - hamburger</t>
+  </si>
+  <si>
+    <t>Q1H_avg</t>
+  </si>
+  <si>
+    <t>Q2H_avg</t>
+  </si>
+  <si>
+    <t>Q3H_avg</t>
+  </si>
+  <si>
+    <t>Q4H_avg</t>
+  </si>
+  <si>
+    <t>Q1M_avg</t>
+  </si>
+  <si>
+    <t>Q2M_avg</t>
   </si>
 </sst>
 </file>
@@ -379,16 +416,16 @@
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -407,6 +444,1803 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Hamburger</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> - Breakup Correlation by Quarters</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.2944444444444427E-2"/>
+          <c:y val="3.7037037037037035E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'quarterly correlation'!$A$8:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Q1 - hamburger</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Q2 - hamburger</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Q3 - hamburger</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Q4 - hamburger</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'quarterly correlation'!$B$8:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.6326691863895334</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.19884986694710483</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.4023404823051253E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.23394813913615528</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9A69-6346-BCFF-03E08093FF4C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1659625791"/>
+        <c:axId val="1643621103"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1659625791"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1643621103"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1643621103"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1659625791"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Milkshake</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> - Breakeup Correlation by Quarters</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'quarterly correlation'!$D$8:$D$11</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Q1 - milkshake</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Q2 - milkshake</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Q2 - milkshake</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Q2 - milkshake</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'quarterly correlation'!$E$8:$E$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>-0.21123070884037842</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.30814801739309577</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.4607694222079899E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.13962954419394971</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5750-9047-989D-571A0F3BA1A6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1765512639"/>
+        <c:axId val="1765514351"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1765512639"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1765514351"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1765514351"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1765512639"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{317EF592-3950-5D62-3E31-431221A9064D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>558800</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97ACD4C8-F624-C144-D162-C0600AC32C85}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -776,7 +2610,7 @@
       <c r="L1" s="11"/>
     </row>
     <row r="2" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="12">
+      <c r="A2" s="14">
         <v>1</v>
       </c>
       <c r="B2" s="5">
@@ -798,7 +2632,7 @@
       <c r="I2" s="9"/>
     </row>
     <row r="3" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12"/>
+      <c r="A3" s="14"/>
       <c r="B3" s="5">
         <v>2</v>
       </c>
@@ -817,7 +2651,7 @@
       <c r="G3" s="8"/>
     </row>
     <row r="4" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="12"/>
+      <c r="A4" s="14"/>
       <c r="B4" s="5">
         <v>3</v>
       </c>
@@ -836,7 +2670,7 @@
       <c r="G4" s="8"/>
     </row>
     <row r="5" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
+      <c r="A5" s="14"/>
       <c r="B5" s="5">
         <v>4</v>
       </c>
@@ -855,7 +2689,7 @@
       <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="12"/>
+      <c r="A6" s="14"/>
       <c r="B6" s="5">
         <v>5</v>
       </c>
@@ -874,7 +2708,7 @@
       <c r="G6" s="8"/>
     </row>
     <row r="7" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="12"/>
+      <c r="A7" s="14"/>
       <c r="B7" s="5">
         <v>6</v>
       </c>
@@ -893,7 +2727,7 @@
       <c r="G7" s="8"/>
     </row>
     <row r="8" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
+      <c r="A8" s="14"/>
       <c r="B8" s="5">
         <v>7</v>
       </c>
@@ -912,7 +2746,7 @@
       <c r="G8" s="8"/>
     </row>
     <row r="9" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
+      <c r="A9" s="14"/>
       <c r="B9" s="5">
         <v>8</v>
       </c>
@@ -931,7 +2765,7 @@
       <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
+      <c r="A10" s="14"/>
       <c r="B10" s="5">
         <v>9</v>
       </c>
@@ -950,7 +2784,7 @@
       <c r="G10" s="8"/>
     </row>
     <row r="11" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
+      <c r="A11" s="14"/>
       <c r="B11" s="5">
         <v>10</v>
       </c>
@@ -969,7 +2803,7 @@
       <c r="G11" s="8"/>
     </row>
     <row r="12" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
+      <c r="A12" s="14"/>
       <c r="B12" s="5">
         <v>11</v>
       </c>
@@ -988,7 +2822,7 @@
       <c r="G12" s="8"/>
     </row>
     <row r="13" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="5">
         <v>12</v>
       </c>
@@ -1007,7 +2841,7 @@
       <c r="G13" s="8"/>
     </row>
     <row r="14" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="12">
+      <c r="A14" s="14">
         <v>2</v>
       </c>
       <c r="B14" s="5">
@@ -1028,7 +2862,7 @@
       <c r="G14" s="8"/>
     </row>
     <row r="15" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
+      <c r="A15" s="14"/>
       <c r="B15" s="5">
         <v>14</v>
       </c>
@@ -1047,7 +2881,7 @@
       <c r="G15" s="8"/>
     </row>
     <row r="16" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
+      <c r="A16" s="14"/>
       <c r="B16" s="5">
         <v>15</v>
       </c>
@@ -1066,7 +2900,7 @@
       <c r="G16" s="8"/>
     </row>
     <row r="17" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
+      <c r="A17" s="14"/>
       <c r="B17" s="5">
         <v>16</v>
       </c>
@@ -1085,7 +2919,7 @@
       <c r="G17" s="8"/>
     </row>
     <row r="18" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
+      <c r="A18" s="14"/>
       <c r="B18" s="5">
         <v>17</v>
       </c>
@@ -1104,7 +2938,7 @@
       <c r="G18" s="8"/>
     </row>
     <row r="19" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
+      <c r="A19" s="14"/>
       <c r="B19" s="5">
         <v>18</v>
       </c>
@@ -1123,7 +2957,7 @@
       <c r="G19" s="8"/>
     </row>
     <row r="20" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
+      <c r="A20" s="14"/>
       <c r="B20" s="5">
         <v>19</v>
       </c>
@@ -1142,7 +2976,7 @@
       <c r="G20" s="8"/>
     </row>
     <row r="21" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12"/>
+      <c r="A21" s="14"/>
       <c r="B21" s="5">
         <v>20</v>
       </c>
@@ -1161,7 +2995,7 @@
       <c r="G21" s="8"/>
     </row>
     <row r="22" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="12"/>
+      <c r="A22" s="14"/>
       <c r="B22" s="5">
         <v>21</v>
       </c>
@@ -1180,7 +3014,7 @@
       <c r="G22" s="8"/>
     </row>
     <row r="23" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="12"/>
+      <c r="A23" s="14"/>
       <c r="B23" s="5">
         <v>22</v>
       </c>
@@ -1199,7 +3033,7 @@
       <c r="G23" s="8"/>
     </row>
     <row r="24" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="12"/>
+      <c r="A24" s="14"/>
       <c r="B24" s="5">
         <v>23</v>
       </c>
@@ -1218,7 +3052,7 @@
       <c r="G24" s="8"/>
     </row>
     <row r="25" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12"/>
+      <c r="A25" s="14"/>
       <c r="B25" s="5">
         <v>24</v>
       </c>
@@ -1237,7 +3071,7 @@
       <c r="G25" s="8"/>
     </row>
     <row r="26" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="12"/>
+      <c r="A26" s="14"/>
       <c r="B26" s="5">
         <v>25</v>
       </c>
@@ -1256,7 +3090,7 @@
       <c r="G26" s="8"/>
     </row>
     <row r="27" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="12">
+      <c r="A27" s="14">
         <v>3</v>
       </c>
       <c r="B27" s="5">
@@ -1277,7 +3111,7 @@
       <c r="G27" s="8"/>
     </row>
     <row r="28" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="12"/>
+      <c r="A28" s="14"/>
       <c r="B28" s="5">
         <v>27</v>
       </c>
@@ -1296,7 +3130,7 @@
       <c r="G28" s="8"/>
     </row>
     <row r="29" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="12"/>
+      <c r="A29" s="14"/>
       <c r="B29" s="5">
         <v>28</v>
       </c>
@@ -1315,7 +3149,7 @@
       <c r="G29" s="8"/>
     </row>
     <row r="30" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="12"/>
+      <c r="A30" s="14"/>
       <c r="B30" s="5">
         <v>29</v>
       </c>
@@ -1334,7 +3168,7 @@
       <c r="G30" s="8"/>
     </row>
     <row r="31" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="12"/>
+      <c r="A31" s="14"/>
       <c r="B31" s="5">
         <v>30</v>
       </c>
@@ -1353,7 +3187,7 @@
       <c r="G31" s="8"/>
     </row>
     <row r="32" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="12"/>
+      <c r="A32" s="14"/>
       <c r="B32" s="5">
         <v>31</v>
       </c>
@@ -1372,7 +3206,7 @@
       <c r="G32" s="8"/>
     </row>
     <row r="33" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="12"/>
+      <c r="A33" s="14"/>
       <c r="B33" s="5">
         <v>32</v>
       </c>
@@ -1391,7 +3225,7 @@
       <c r="G33" s="8"/>
     </row>
     <row r="34" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="12"/>
+      <c r="A34" s="14"/>
       <c r="B34" s="5">
         <v>33</v>
       </c>
@@ -1410,7 +3244,7 @@
       <c r="G34" s="8"/>
     </row>
     <row r="35" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="12"/>
+      <c r="A35" s="14"/>
       <c r="B35" s="5">
         <v>34</v>
       </c>
@@ -1429,7 +3263,7 @@
       <c r="G35" s="8"/>
     </row>
     <row r="36" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="12"/>
+      <c r="A36" s="14"/>
       <c r="B36" s="5">
         <v>35</v>
       </c>
@@ -1448,7 +3282,7 @@
       <c r="G36" s="8"/>
     </row>
     <row r="37" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="12"/>
+      <c r="A37" s="14"/>
       <c r="B37" s="5">
         <v>36</v>
       </c>
@@ -1467,7 +3301,7 @@
       <c r="G37" s="8"/>
     </row>
     <row r="38" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="12"/>
+      <c r="A38" s="14"/>
       <c r="B38" s="5">
         <v>37</v>
       </c>
@@ -1486,7 +3320,7 @@
       <c r="G38" s="8"/>
     </row>
     <row r="39" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="12"/>
+      <c r="A39" s="14"/>
       <c r="B39" s="5">
         <v>38</v>
       </c>
@@ -1505,7 +3339,7 @@
       <c r="G39" s="8"/>
     </row>
     <row r="40" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="12"/>
+      <c r="A40" s="14"/>
       <c r="B40" s="5">
         <v>39</v>
       </c>
@@ -1524,7 +3358,7 @@
       <c r="G40" s="8"/>
     </row>
     <row r="41" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="12">
+      <c r="A41" s="14">
         <v>4</v>
       </c>
       <c r="B41" s="5">
@@ -1545,7 +3379,7 @@
       <c r="G41" s="8"/>
     </row>
     <row r="42" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="12"/>
+      <c r="A42" s="14"/>
       <c r="B42" s="5">
         <v>41</v>
       </c>
@@ -1564,7 +3398,7 @@
       <c r="G42" s="8"/>
     </row>
     <row r="43" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="12"/>
+      <c r="A43" s="14"/>
       <c r="B43" s="5">
         <v>42</v>
       </c>
@@ -1583,7 +3417,7 @@
       <c r="G43" s="8"/>
     </row>
     <row r="44" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="12"/>
+      <c r="A44" s="14"/>
       <c r="B44" s="5">
         <v>43</v>
       </c>
@@ -1602,7 +3436,7 @@
       <c r="G44" s="8"/>
     </row>
     <row r="45" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="12"/>
+      <c r="A45" s="14"/>
       <c r="B45" s="5">
         <v>44</v>
       </c>
@@ -1621,7 +3455,7 @@
       <c r="G45" s="8"/>
     </row>
     <row r="46" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="12"/>
+      <c r="A46" s="14"/>
       <c r="B46" s="5">
         <v>45</v>
       </c>
@@ -1640,7 +3474,7 @@
       <c r="G46" s="8"/>
     </row>
     <row r="47" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="12"/>
+      <c r="A47" s="14"/>
       <c r="B47" s="5">
         <v>46</v>
       </c>
@@ -1659,7 +3493,7 @@
       <c r="G47" s="8"/>
     </row>
     <row r="48" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="12"/>
+      <c r="A48" s="14"/>
       <c r="B48" s="5">
         <v>47</v>
       </c>
@@ -1678,7 +3512,7 @@
       <c r="G48" s="8"/>
     </row>
     <row r="49" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="12"/>
+      <c r="A49" s="14"/>
       <c r="B49" s="5">
         <v>48</v>
       </c>
@@ -1697,7 +3531,7 @@
       <c r="G49" s="8"/>
     </row>
     <row r="50" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="12"/>
+      <c r="A50" s="14"/>
       <c r="B50" s="5">
         <v>49</v>
       </c>
@@ -1716,7 +3550,7 @@
       <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="12"/>
+      <c r="A51" s="14"/>
       <c r="B51" s="5">
         <v>50</v>
       </c>
@@ -1735,7 +3569,7 @@
       <c r="G51" s="8"/>
     </row>
     <row r="52" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="12"/>
+      <c r="A52" s="14"/>
       <c r="B52" s="5">
         <v>51</v>
       </c>
@@ -1754,7 +3588,7 @@
       <c r="G52" s="8"/>
     </row>
     <row r="53" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="12"/>
+      <c r="A53" s="14"/>
       <c r="B53" s="5">
         <v>52</v>
       </c>
@@ -1773,7 +3607,7 @@
       <c r="G53" s="8"/>
     </row>
     <row r="54" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="12"/>
+      <c r="A54" s="14"/>
       <c r="B54" s="5">
         <v>53</v>
       </c>
@@ -1812,24 +3646,24 @@
     <col min="5" max="53" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="14">
+      <c r="B1" s="15">
         <v>1</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
       <c r="N1" s="16">
         <v>2</v>
       </c>
@@ -1845,22 +3679,22 @@
       <c r="X1" s="16"/>
       <c r="Y1" s="16"/>
       <c r="Z1" s="16"/>
-      <c r="AA1" s="14">
+      <c r="AA1" s="15">
         <v>3</v>
       </c>
-      <c r="AB1" s="14"/>
-      <c r="AC1" s="14"/>
-      <c r="AD1" s="14"/>
-      <c r="AE1" s="14"/>
-      <c r="AF1" s="14"/>
-      <c r="AG1" s="14"/>
-      <c r="AH1" s="14"/>
-      <c r="AI1" s="14"/>
-      <c r="AJ1" s="14"/>
-      <c r="AK1" s="14"/>
-      <c r="AL1" s="14"/>
-      <c r="AM1" s="14"/>
-      <c r="AN1" s="14"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15"/>
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15"/>
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15"/>
       <c r="AO1" s="16">
         <v>4</v>
       </c>
@@ -2995,4 +4829,1305 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D312562-73FC-5743-9571-F0CD42E073D0}">
+  <dimension ref="A1:BB54"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="53" width="10.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="15">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="16">
+        <v>2</v>
+      </c>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="15">
+        <v>3</v>
+      </c>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15"/>
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15"/>
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15"/>
+      <c r="AO1" s="16">
+        <v>4</v>
+      </c>
+      <c r="AP1" s="16"/>
+      <c r="AQ1" s="16"/>
+      <c r="AR1" s="16"/>
+      <c r="AS1" s="16"/>
+      <c r="AT1" s="16"/>
+      <c r="AU1" s="16"/>
+      <c r="AV1" s="16"/>
+      <c r="AW1" s="16"/>
+      <c r="AX1" s="16"/>
+      <c r="AY1" s="16"/>
+      <c r="AZ1" s="16"/>
+      <c r="BA1" s="16"/>
+      <c r="BB1" s="16"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5">
+        <v>2</v>
+      </c>
+      <c r="D2" s="5">
+        <v>3</v>
+      </c>
+      <c r="E2" s="5">
+        <v>4</v>
+      </c>
+      <c r="F2" s="5">
+        <v>5</v>
+      </c>
+      <c r="G2" s="5">
+        <v>6</v>
+      </c>
+      <c r="H2" s="5">
+        <v>7</v>
+      </c>
+      <c r="I2" s="5">
+        <v>8</v>
+      </c>
+      <c r="J2" s="5">
+        <v>9</v>
+      </c>
+      <c r="K2" s="5">
+        <v>10</v>
+      </c>
+      <c r="L2" s="5">
+        <v>11</v>
+      </c>
+      <c r="M2" s="5">
+        <v>12</v>
+      </c>
+      <c r="N2" s="5">
+        <v>13</v>
+      </c>
+      <c r="O2" s="5">
+        <v>14</v>
+      </c>
+      <c r="P2" s="5">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>16</v>
+      </c>
+      <c r="R2" s="5">
+        <v>17</v>
+      </c>
+      <c r="S2" s="5">
+        <v>18</v>
+      </c>
+      <c r="T2" s="5">
+        <v>19</v>
+      </c>
+      <c r="U2" s="5">
+        <v>20</v>
+      </c>
+      <c r="V2" s="5">
+        <v>21</v>
+      </c>
+      <c r="W2" s="5">
+        <v>22</v>
+      </c>
+      <c r="X2" s="5">
+        <v>23</v>
+      </c>
+      <c r="Y2" s="5">
+        <v>24</v>
+      </c>
+      <c r="Z2" s="5">
+        <v>25</v>
+      </c>
+      <c r="AA2" s="5">
+        <v>26</v>
+      </c>
+      <c r="AB2" s="5">
+        <v>27</v>
+      </c>
+      <c r="AC2" s="5">
+        <v>28</v>
+      </c>
+      <c r="AD2" s="5">
+        <v>29</v>
+      </c>
+      <c r="AE2" s="5">
+        <v>30</v>
+      </c>
+      <c r="AF2" s="5">
+        <v>31</v>
+      </c>
+      <c r="AG2" s="5">
+        <v>32</v>
+      </c>
+      <c r="AH2" s="5">
+        <v>33</v>
+      </c>
+      <c r="AI2" s="5">
+        <v>34</v>
+      </c>
+      <c r="AJ2" s="5">
+        <v>35</v>
+      </c>
+      <c r="AK2" s="5">
+        <v>36</v>
+      </c>
+      <c r="AL2" s="5">
+        <v>37</v>
+      </c>
+      <c r="AM2" s="5">
+        <v>38</v>
+      </c>
+      <c r="AN2" s="5">
+        <v>39</v>
+      </c>
+      <c r="AO2" s="5">
+        <v>40</v>
+      </c>
+      <c r="AP2" s="5">
+        <v>41</v>
+      </c>
+      <c r="AQ2" s="5">
+        <v>42</v>
+      </c>
+      <c r="AR2" s="5">
+        <v>43</v>
+      </c>
+      <c r="AS2" s="5">
+        <v>44</v>
+      </c>
+      <c r="AT2" s="5">
+        <v>45</v>
+      </c>
+      <c r="AU2" s="5">
+        <v>46</v>
+      </c>
+      <c r="AV2" s="5">
+        <v>47</v>
+      </c>
+      <c r="AW2" s="5">
+        <v>48</v>
+      </c>
+      <c r="AX2" s="5">
+        <v>49</v>
+      </c>
+      <c r="AY2" s="5">
+        <v>50</v>
+      </c>
+      <c r="AZ2" s="5">
+        <v>51</v>
+      </c>
+      <c r="BA2" s="5">
+        <v>52</v>
+      </c>
+      <c r="BB2" s="5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="R3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="T3" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="U3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="V3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="W3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="X3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y3" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z3" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA3" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB3" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD3" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE3" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF3" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG3" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH3" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI3" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="AJ3" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK3" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="AL3" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="AM3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AN3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="AO3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AP3" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AQ3" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="AR3" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="AS3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT3" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU3" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AV3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AW3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="AX3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="AY3" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="AZ3" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="BA3" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="BB3" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="8">
+        <v>71</v>
+      </c>
+      <c r="C4" s="8">
+        <v>76</v>
+      </c>
+      <c r="D4" s="8">
+        <v>69</v>
+      </c>
+      <c r="E4" s="8">
+        <v>73</v>
+      </c>
+      <c r="F4" s="8">
+        <v>73</v>
+      </c>
+      <c r="G4" s="8">
+        <v>69</v>
+      </c>
+      <c r="H4" s="8">
+        <v>69</v>
+      </c>
+      <c r="I4" s="8">
+        <v>70</v>
+      </c>
+      <c r="J4" s="8">
+        <v>66</v>
+      </c>
+      <c r="K4" s="8">
+        <v>67</v>
+      </c>
+      <c r="L4" s="8">
+        <v>68</v>
+      </c>
+      <c r="M4" s="8">
+        <v>72</v>
+      </c>
+      <c r="N4" s="8">
+        <v>67</v>
+      </c>
+      <c r="O4" s="8">
+        <v>75</v>
+      </c>
+      <c r="P4" s="8">
+        <v>71</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>71</v>
+      </c>
+      <c r="R4" s="8">
+        <v>82</v>
+      </c>
+      <c r="S4" s="8">
+        <v>100</v>
+      </c>
+      <c r="T4" s="8">
+        <v>77</v>
+      </c>
+      <c r="U4" s="8">
+        <v>73</v>
+      </c>
+      <c r="V4" s="8">
+        <v>75</v>
+      </c>
+      <c r="W4" s="8">
+        <v>74</v>
+      </c>
+      <c r="X4" s="8">
+        <v>92</v>
+      </c>
+      <c r="Y4" s="8">
+        <v>69</v>
+      </c>
+      <c r="Z4" s="8">
+        <v>72</v>
+      </c>
+      <c r="AA4" s="8">
+        <v>70</v>
+      </c>
+      <c r="AB4" s="8">
+        <v>69</v>
+      </c>
+      <c r="AC4" s="8">
+        <v>72</v>
+      </c>
+      <c r="AD4" s="8">
+        <v>75</v>
+      </c>
+      <c r="AE4" s="8">
+        <v>78</v>
+      </c>
+      <c r="AF4" s="8">
+        <v>72</v>
+      </c>
+      <c r="AG4" s="8">
+        <v>72</v>
+      </c>
+      <c r="AH4" s="8">
+        <v>68</v>
+      </c>
+      <c r="AI4" s="8">
+        <v>74</v>
+      </c>
+      <c r="AJ4" s="8">
+        <v>67</v>
+      </c>
+      <c r="AK4" s="8">
+        <v>63</v>
+      </c>
+      <c r="AL4" s="8">
+        <v>72</v>
+      </c>
+      <c r="AM4" s="8">
+        <v>66</v>
+      </c>
+      <c r="AN4" s="8">
+        <v>72</v>
+      </c>
+      <c r="AO4" s="8">
+        <v>66</v>
+      </c>
+      <c r="AP4" s="8">
+        <v>61</v>
+      </c>
+      <c r="AQ4" s="8">
+        <v>67</v>
+      </c>
+      <c r="AR4" s="8">
+        <v>67</v>
+      </c>
+      <c r="AS4" s="8">
+        <v>54</v>
+      </c>
+      <c r="AT4" s="8">
+        <v>61</v>
+      </c>
+      <c r="AU4" s="8">
+        <v>61</v>
+      </c>
+      <c r="AV4" s="8">
+        <v>63</v>
+      </c>
+      <c r="AW4" s="8">
+        <v>56</v>
+      </c>
+      <c r="AX4" s="8">
+        <v>72</v>
+      </c>
+      <c r="AY4" s="8">
+        <v>74</v>
+      </c>
+      <c r="AZ4" s="8">
+        <v>75</v>
+      </c>
+      <c r="BA4" s="8">
+        <v>78</v>
+      </c>
+      <c r="BB4" s="8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="7">
+        <v>24</v>
+      </c>
+      <c r="C5" s="7">
+        <v>22</v>
+      </c>
+      <c r="D5" s="7">
+        <v>19</v>
+      </c>
+      <c r="E5" s="7">
+        <v>23</v>
+      </c>
+      <c r="F5" s="7">
+        <v>21</v>
+      </c>
+      <c r="G5" s="7">
+        <v>23</v>
+      </c>
+      <c r="H5" s="7">
+        <v>25</v>
+      </c>
+      <c r="I5" s="7">
+        <v>23</v>
+      </c>
+      <c r="J5" s="7">
+        <v>26</v>
+      </c>
+      <c r="K5" s="7">
+        <v>22</v>
+      </c>
+      <c r="L5" s="7">
+        <v>22</v>
+      </c>
+      <c r="M5" s="7">
+        <v>26</v>
+      </c>
+      <c r="N5" s="7">
+        <v>25</v>
+      </c>
+      <c r="O5" s="7">
+        <v>24</v>
+      </c>
+      <c r="P5" s="7">
+        <v>23</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>22</v>
+      </c>
+      <c r="R5" s="7">
+        <v>25</v>
+      </c>
+      <c r="S5" s="7">
+        <v>27</v>
+      </c>
+      <c r="T5" s="7">
+        <v>31</v>
+      </c>
+      <c r="U5" s="7">
+        <v>28</v>
+      </c>
+      <c r="V5" s="7">
+        <v>30</v>
+      </c>
+      <c r="W5" s="7">
+        <v>30</v>
+      </c>
+      <c r="X5" s="7">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="7">
+        <v>29</v>
+      </c>
+      <c r="Z5" s="7">
+        <v>29</v>
+      </c>
+      <c r="AA5" s="7">
+        <v>26</v>
+      </c>
+      <c r="AB5" s="7">
+        <v>27</v>
+      </c>
+      <c r="AC5" s="7">
+        <v>25</v>
+      </c>
+      <c r="AD5" s="7">
+        <v>41</v>
+      </c>
+      <c r="AE5" s="7">
+        <v>31</v>
+      </c>
+      <c r="AF5" s="7">
+        <v>30</v>
+      </c>
+      <c r="AG5" s="7">
+        <v>26</v>
+      </c>
+      <c r="AH5" s="7">
+        <v>25</v>
+      </c>
+      <c r="AI5" s="7">
+        <v>22</v>
+      </c>
+      <c r="AJ5" s="7">
+        <v>22</v>
+      </c>
+      <c r="AK5" s="7">
+        <v>21</v>
+      </c>
+      <c r="AL5" s="7">
+        <v>23</v>
+      </c>
+      <c r="AM5" s="7">
+        <v>22</v>
+      </c>
+      <c r="AN5" s="7">
+        <v>22</v>
+      </c>
+      <c r="AO5" s="7">
+        <v>20</v>
+      </c>
+      <c r="AP5" s="7">
+        <v>22</v>
+      </c>
+      <c r="AQ5" s="7">
+        <v>28</v>
+      </c>
+      <c r="AR5" s="7">
+        <v>24</v>
+      </c>
+      <c r="AS5" s="7">
+        <v>22</v>
+      </c>
+      <c r="AT5" s="7">
+        <v>21</v>
+      </c>
+      <c r="AU5" s="7">
+        <v>21</v>
+      </c>
+      <c r="AV5" s="7">
+        <v>20</v>
+      </c>
+      <c r="AW5" s="7">
+        <v>23</v>
+      </c>
+      <c r="AX5" s="7">
+        <v>25</v>
+      </c>
+      <c r="AY5" s="7">
+        <v>22</v>
+      </c>
+      <c r="AZ5" s="7">
+        <v>21</v>
+      </c>
+      <c r="BA5" s="7">
+        <v>22</v>
+      </c>
+      <c r="BB5" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="8">
+        <v>19</v>
+      </c>
+      <c r="C6" s="8">
+        <v>42</v>
+      </c>
+      <c r="D6" s="8">
+        <v>22</v>
+      </c>
+      <c r="E6" s="8">
+        <v>19</v>
+      </c>
+      <c r="F6" s="8">
+        <v>18</v>
+      </c>
+      <c r="G6" s="8">
+        <v>19</v>
+      </c>
+      <c r="H6" s="8">
+        <v>20</v>
+      </c>
+      <c r="I6" s="8">
+        <v>19</v>
+      </c>
+      <c r="J6" s="8">
+        <v>18</v>
+      </c>
+      <c r="K6" s="8">
+        <v>18</v>
+      </c>
+      <c r="L6" s="8">
+        <v>18</v>
+      </c>
+      <c r="M6" s="8">
+        <v>19</v>
+      </c>
+      <c r="N6" s="8">
+        <v>19</v>
+      </c>
+      <c r="O6" s="8">
+        <v>19</v>
+      </c>
+      <c r="P6" s="8">
+        <v>19</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>17</v>
+      </c>
+      <c r="R6" s="8">
+        <v>18</v>
+      </c>
+      <c r="S6" s="8">
+        <v>18</v>
+      </c>
+      <c r="T6" s="8">
+        <v>19</v>
+      </c>
+      <c r="U6" s="8">
+        <v>18</v>
+      </c>
+      <c r="V6" s="8">
+        <v>22</v>
+      </c>
+      <c r="W6" s="8">
+        <v>20</v>
+      </c>
+      <c r="X6" s="8">
+        <v>17</v>
+      </c>
+      <c r="Y6" s="8">
+        <v>17</v>
+      </c>
+      <c r="Z6" s="8">
+        <v>18</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>18</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>18</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>18</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>20</v>
+      </c>
+      <c r="AE6" s="8">
+        <v>19</v>
+      </c>
+      <c r="AF6" s="8">
+        <v>19</v>
+      </c>
+      <c r="AG6" s="8">
+        <v>34</v>
+      </c>
+      <c r="AH6" s="8">
+        <v>19</v>
+      </c>
+      <c r="AI6" s="8">
+        <v>18</v>
+      </c>
+      <c r="AJ6" s="8">
+        <v>18</v>
+      </c>
+      <c r="AK6" s="8">
+        <v>21</v>
+      </c>
+      <c r="AL6" s="8">
+        <v>18</v>
+      </c>
+      <c r="AM6" s="8">
+        <v>18</v>
+      </c>
+      <c r="AN6" s="8">
+        <v>21</v>
+      </c>
+      <c r="AO6" s="8">
+        <v>18</v>
+      </c>
+      <c r="AP6" s="8">
+        <v>19</v>
+      </c>
+      <c r="AQ6" s="8">
+        <v>19</v>
+      </c>
+      <c r="AR6" s="8">
+        <v>20</v>
+      </c>
+      <c r="AS6" s="8">
+        <v>18</v>
+      </c>
+      <c r="AT6" s="8">
+        <v>19</v>
+      </c>
+      <c r="AU6" s="8">
+        <v>22</v>
+      </c>
+      <c r="AV6" s="8">
+        <v>18</v>
+      </c>
+      <c r="AW6" s="8">
+        <v>19</v>
+      </c>
+      <c r="AX6" s="8">
+        <v>20</v>
+      </c>
+      <c r="AY6" s="8">
+        <v>20</v>
+      </c>
+      <c r="AZ6" s="8">
+        <v>19</v>
+      </c>
+      <c r="BA6" s="8">
+        <v>18</v>
+      </c>
+      <c r="BB6" s="8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A7" s="10"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8"/>
+    </row>
+    <row r="8" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="8">
+        <f>CORREL(B6:M6,B4:M4)</f>
+        <v>0.6326691863895334</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8">
+        <f>CORREL(B5:M5,B6:M6)</f>
+        <v>-0.21123070884037842</v>
+      </c>
+      <c r="G8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8">
+        <f>AVERAGE(B4:M4)</f>
+        <v>70.25</v>
+      </c>
+      <c r="J8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K8">
+        <f>AVERAGE(B5:M5)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="8">
+        <f>CORREL(N4:Z4,N6:Z6)</f>
+        <v>-0.19884986694710483</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9">
+        <f>CORREL(N5:Z5,N6:Z6)</f>
+        <v>0.30814801739309577</v>
+      </c>
+      <c r="G9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9">
+        <f>AVERAGE(N4:Z4)</f>
+        <v>76.769230769230774</v>
+      </c>
+      <c r="J9" t="s">
+        <v>72</v>
+      </c>
+      <c r="K9">
+        <f>AVERAGE(N5:Z5)</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="8">
+        <f>CORREL(AA4:AN4,AA6:AN6)</f>
+        <v>7.4023404823051253E-2</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10">
+        <f>CORREL(AA6:AN6,AA5:AN5)</f>
+        <v>4.4607694222079899E-2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10">
+        <f>AVERAGE(AA4:AN4)</f>
+        <v>70.714285714285708</v>
+      </c>
+      <c r="J10" t="s">
+        <v>72</v>
+      </c>
+      <c r="K10">
+        <f>AVERAGE(AA5:AN5)</f>
+        <v>25.928571428571427</v>
+      </c>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="8">
+        <f>CORREL(AO4:BB4,AO6:BB6)</f>
+        <v>0.23394813913615528</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11">
+        <f>CORREL(AO5:BB5,AO6:BB6)</f>
+        <v>-0.13962954419394971</v>
+      </c>
+      <c r="G11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11">
+        <f>AVERAGE(AO4:BB4)</f>
+        <v>66.285714285714292</v>
+      </c>
+      <c r="J11" t="s">
+        <v>72</v>
+      </c>
+      <c r="K11">
+        <f>AVERAGE(AO5:BB5)</f>
+        <v>22.214285714285715</v>
+      </c>
+    </row>
+    <row r="12" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A12" s="10"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="8"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A13" s="10"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="8"/>
+      <c r="G13" t="e">
+        <f>VLOOKUP('quarterly correlation'!B4, 'by search term'!B:C,3, 71)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A14" s="10"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A15" s="10"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="8"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A16" s="10"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="8"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="10"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="8"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="10"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="10"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="8"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="10"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="8"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="10"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="8"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="10"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="10"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="8"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="10"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="8"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="10"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="8"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="10"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="10"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="8"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="10"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="8"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="10"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="10"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="10"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="8"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="10"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="8"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="10"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="8"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="10"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="8"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="10"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="8"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="10"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="8"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="10"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="8"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="10"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="8"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="10"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="8"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="10"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="8"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="10"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="8"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="10"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="8"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" s="10"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="8"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="10"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="8"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="10"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="8"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="10"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="8"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="10"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="8"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="10"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="8"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="10"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="8"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="10"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="8"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="10"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="8"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="10"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="8"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="10"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="8"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="10"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="N1:Z1"/>
+    <mergeCell ref="AA1:AN1"/>
+    <mergeCell ref="AO1:BB1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>